--- a/VtigerPlaywright/TestData/dataBaseVtiger.xlsx
+++ b/VtigerPlaywright/TestData/dataBaseVtiger.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3d5ec3308cc1e089/Desktop/TortoiseGit/palywright/VtigerPlaywright/TestData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19308F30-AD15-44A9-8817-724E03855855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{19308F30-AD15-44A9-8817-724E03855855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD5A79C5-2B9C-42F5-BF2B-D274E812D234}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{5F25CB26-4AFA-45ED-A7E8-3D62C9CDB872}"/>
+    <workbookView xWindow="3440" yWindow="2720" windowWidth="14400" windowHeight="7360" xr2:uid="{5F25CB26-4AFA-45ED-A7E8-3D62C9CDB872}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" r:id="rId1"/>
@@ -36,24 +36,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
   <si>
-    <t>ExpectedResult</t>
-  </si>
-  <si>
-    <t>ThemeLabel</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>Username</t>
-  </si>
-  <si>
-    <t>Url</t>
-  </si>
-  <si>
-    <t>TestCaseID</t>
-  </si>
-  <si>
     <t>TC_001</t>
   </si>
   <si>
@@ -96,13 +78,31 @@
     <t>/Home/</t>
   </si>
   <si>
-    <t>Result</t>
-  </si>
-  <si>
     <t>fail</t>
   </si>
   <si>
     <t>success</t>
+  </si>
+  <si>
+    <t>testCaseID</t>
+  </si>
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>themeLabel</t>
+  </si>
+  <si>
+    <t>expectedResult</t>
+  </si>
+  <si>
+    <t>result</t>
   </si>
 </sst>
 </file>
@@ -504,117 +504,117 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" t="s">
-        <v>19</v>
-      </c>
       <c r="G4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
